--- a/video_gen_eval/templates/visual_arts_eval.xlsx
+++ b/video_gen_eval/templates/visual_arts_eval.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Evaluation" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evaluation" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -546,7 +546,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W15"/>
+  <dimension ref="A1:X15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -607,85 +607,90 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>ground_truth / criteria</t>
+          <t>ground_truth</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>criteria</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>error_examples</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="J1" s="2" t="inlineStr">
         <is>
           <t>veo31_video</t>
         </is>
       </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="K1" s="2" t="inlineStr">
         <is>
           <t>veo31_score</t>
         </is>
       </c>
-      <c r="K1" s="2" t="inlineStr">
+      <c r="L1" s="2" t="inlineStr">
         <is>
           <t>veo31_notes</t>
         </is>
       </c>
-      <c r="L1" s="3" t="inlineStr">
+      <c r="M1" s="3" t="inlineStr">
         <is>
           <t>sora2_video</t>
         </is>
       </c>
-      <c r="M1" s="3" t="inlineStr">
+      <c r="N1" s="3" t="inlineStr">
         <is>
           <t>sora2_score</t>
         </is>
       </c>
-      <c r="N1" s="3" t="inlineStr">
+      <c r="O1" s="3" t="inlineStr">
         <is>
           <t>sora2_notes</t>
         </is>
       </c>
-      <c r="O1" s="4" t="inlineStr">
+      <c r="P1" s="4" t="inlineStr">
         <is>
           <t>kling3_video</t>
         </is>
       </c>
-      <c r="P1" s="4" t="inlineStr">
+      <c r="Q1" s="4" t="inlineStr">
         <is>
           <t>kling3_score</t>
         </is>
       </c>
-      <c r="Q1" s="4" t="inlineStr">
+      <c r="R1" s="4" t="inlineStr">
         <is>
           <t>kling3_notes</t>
         </is>
       </c>
-      <c r="R1" s="5" t="inlineStr">
+      <c r="S1" s="5" t="inlineStr">
         <is>
           <t>wan22_video</t>
         </is>
       </c>
-      <c r="S1" s="5" t="inlineStr">
+      <c r="T1" s="5" t="inlineStr">
         <is>
           <t>wan22_score</t>
         </is>
       </c>
-      <c r="T1" s="5" t="inlineStr">
+      <c r="U1" s="5" t="inlineStr">
         <is>
           <t>wan22_notes</t>
         </is>
       </c>
-      <c r="U1" s="6" t="inlineStr">
+      <c r="V1" s="6" t="inlineStr">
         <is>
           <t>wan26_video</t>
         </is>
       </c>
-      <c r="V1" s="6" t="inlineStr">
+      <c r="W1" s="6" t="inlineStr">
         <is>
           <t>wan26_score</t>
         </is>
       </c>
-      <c r="W1" s="6" t="inlineStr">
+      <c r="X1" s="6" t="inlineStr">
         <is>
           <t>wan26_notes</t>
         </is>
@@ -725,52 +730,56 @@
       <c r="G2" s="8" t="inlineStr">
         <is>
           <t>Answer: Primary colors (red, blue, yellow) mix to form secondary colors: red+blue=purple, blue+yellow=green, red+yellow=orange
-Key visuals: red, blue, and yellow primary color blobs, mixing animation for each pair, purple result from red+blue, green result from blue+yellow, orange result from red+yellow, labels for each secondary color
-Rubric: The video must correctly display all three primary colors and demonstrate all three mixing combinations yielding the correct secondary colors with clear labels.</t>
+Key visuals: red, blue, and yellow primary color blobs, mixing animation for each pair, purple result from red+blue, green result from blue+yellow, orange result from red+yellow, labels for each secondary color</t>
         </is>
       </c>
       <c r="H2" s="8" t="inlineStr">
+        <is>
+          <t>- The video must correctly display all three primary colors and demonstrate all three mixing combinations yielding the correct secondary colors with clear labels.</t>
+        </is>
+      </c>
+      <c r="I2" s="8" t="inlineStr">
         <is>
           <t>- Showing red + blue = green instead of purple
 - Omitting one of the three mixing combinations
 - Using incorrect primary colors (e.g., including green as a primary)</t>
         </is>
       </c>
-      <c r="I2" s="9" t="inlineStr">
+      <c r="J2" s="9" t="inlineStr">
         <is>
           <t>051_veo31_EVB-Art-ELow-K-CK-F-051.mp4</t>
         </is>
       </c>
-      <c r="J2" s="10" t="inlineStr"/>
-      <c r="K2" s="8" t="inlineStr"/>
-      <c r="L2" s="11" t="inlineStr">
+      <c r="K2" s="10" t="n"/>
+      <c r="L2" s="8" t="n"/>
+      <c r="M2" s="11" t="inlineStr">
         <is>
           <t>051_sora2_EVB-Art-ELow-K-CK-F-051.mp4</t>
         </is>
       </c>
-      <c r="M2" s="10" t="inlineStr"/>
-      <c r="N2" s="8" t="inlineStr"/>
-      <c r="O2" s="12" t="inlineStr">
+      <c r="N2" s="10" t="n"/>
+      <c r="O2" s="8" t="n"/>
+      <c r="P2" s="12" t="inlineStr">
         <is>
           <t>051_kling3_EVB-Art-ELow-K-CK-F-051.mp4</t>
         </is>
       </c>
-      <c r="P2" s="10" t="inlineStr"/>
-      <c r="Q2" s="8" t="inlineStr"/>
-      <c r="R2" s="13" t="inlineStr">
+      <c r="Q2" s="10" t="n"/>
+      <c r="R2" s="8" t="n"/>
+      <c r="S2" s="13" t="inlineStr">
         <is>
           <t>051_wan22_EVB-Art-ELow-K-CK-F-051.mp4</t>
         </is>
       </c>
-      <c r="S2" s="10" t="inlineStr"/>
-      <c r="T2" s="8" t="inlineStr"/>
-      <c r="U2" s="14" t="inlineStr">
+      <c r="T2" s="10" t="n"/>
+      <c r="U2" s="8" t="n"/>
+      <c r="V2" s="14" t="inlineStr">
         <is>
           <t>051_wan26_EVB-Art-ELow-K-CK-F-051.mp4</t>
         </is>
       </c>
-      <c r="V2" s="10" t="inlineStr"/>
-      <c r="W2" s="8" t="inlineStr"/>
+      <c r="W2" s="10" t="n"/>
+      <c r="X2" s="8" t="n"/>
     </row>
     <row r="3" ht="60" customHeight="1">
       <c r="A3" s="7" t="inlineStr">
@@ -806,52 +815,56 @@
       <c r="G3" s="8" t="inlineStr">
         <is>
           <t>Answer: Primary: red, yellow, blue; Secondary: orange, purple, green
-Key visuals: three primary color swatches, mixing animation, three secondary color results
-Rubric: The video must correctly show all three primary colors and demonstrate each mixing pair producing the correct secondary color.</t>
+Key visuals: three primary color swatches, mixing animation, three secondary color results</t>
         </is>
       </c>
       <c r="H3" s="8" t="inlineStr">
+        <is>
+          <t>- The video must correctly show all three primary colors and demonstrate each mixing pair producing the correct secondary color.</t>
+        </is>
+      </c>
+      <c r="I3" s="8" t="inlineStr">
         <is>
           <t>- Wrong secondary color from a mix
 - Using RGB primaries instead of paint primaries
 - Missing one mixing pair</t>
         </is>
       </c>
-      <c r="I3" s="9" t="inlineStr">
+      <c r="J3" s="9" t="inlineStr">
         <is>
           <t>008_veo31_EVB-Art-EHigh-K-CK-F1-008.mp4</t>
         </is>
       </c>
-      <c r="J3" s="10" t="inlineStr"/>
-      <c r="K3" s="8" t="inlineStr"/>
-      <c r="L3" s="11" t="inlineStr">
+      <c r="K3" s="10" t="n"/>
+      <c r="L3" s="8" t="n"/>
+      <c r="M3" s="11" t="inlineStr">
         <is>
           <t>008_sora2_EVB-Art-EHigh-K-CK-F1-008.mp4</t>
         </is>
       </c>
-      <c r="M3" s="10" t="inlineStr"/>
-      <c r="N3" s="8" t="inlineStr"/>
-      <c r="O3" s="12" t="inlineStr">
+      <c r="N3" s="10" t="n"/>
+      <c r="O3" s="8" t="n"/>
+      <c r="P3" s="12" t="inlineStr">
         <is>
           <t>008_kling3_EVB-Art-EHigh-K-CK-F1-008.mp4</t>
         </is>
       </c>
-      <c r="P3" s="10" t="inlineStr"/>
-      <c r="Q3" s="8" t="inlineStr"/>
-      <c r="R3" s="13" t="inlineStr">
+      <c r="Q3" s="10" t="n"/>
+      <c r="R3" s="8" t="n"/>
+      <c r="S3" s="13" t="inlineStr">
         <is>
           <t>008_wan22_EVB-Art-EHigh-K-CK-F1-008.mp4</t>
         </is>
       </c>
-      <c r="S3" s="10" t="inlineStr"/>
-      <c r="T3" s="8" t="inlineStr"/>
-      <c r="U3" s="14" t="inlineStr">
+      <c r="T3" s="10" t="n"/>
+      <c r="U3" s="8" t="n"/>
+      <c r="V3" s="14" t="inlineStr">
         <is>
           <t>008_wan26_EVB-Art-EHigh-K-CK-F1-008.mp4</t>
         </is>
       </c>
-      <c r="V3" s="10" t="inlineStr"/>
-      <c r="W3" s="8" t="inlineStr"/>
+      <c r="W3" s="10" t="n"/>
+      <c r="X3" s="8" t="n"/>
     </row>
     <row r="4" ht="60" customHeight="1">
       <c r="A4" s="7" t="inlineStr">
@@ -887,52 +900,56 @@
       <c r="G4" s="8" t="inlineStr">
         <is>
           <t>Answer: Seven elements of art: line, shape, form, color, value, space, texture — each with a visual example
-Key visuals: line example (straight or curved drawn line), shape example (flat geometric shape), form example (3D object with shading), color example (color wheel segment), value example (grayscale gradient), space example (positive and negative space), texture example (surface close-up), text labels for each element
-Rubric: The video must present all seven elements of art in sequence, each with a correct visual example and a clear text label. No element may be omitted or visually misrepresented.</t>
+Key visuals: line example (straight or curved drawn line), shape example (flat geometric shape), form example (3D object with shading), color example (color wheel segment), value example (grayscale gradient), space example (positive and negative space), texture example (surface close-up), text labels for each element</t>
         </is>
       </c>
       <c r="H4" s="8" t="inlineStr">
+        <is>
+          <t>- The video must present all seven elements of art in sequence, each with a correct visual example and a clear text label. No element may be omitted or visually misrepresented.</t>
+        </is>
+      </c>
+      <c r="I4" s="8" t="inlineStr">
         <is>
           <t>- Omitting one or more of the seven elements
 - Confusing shape (2D) with form (3D)
 - Showing value without a grayscale gradient</t>
         </is>
       </c>
-      <c r="I4" s="9" t="inlineStr">
+      <c r="J4" s="9" t="inlineStr">
         <is>
           <t>052_veo31_EVB-Art-Mid-K-CK-C-052.mp4</t>
         </is>
       </c>
-      <c r="J4" s="10" t="inlineStr"/>
-      <c r="K4" s="8" t="inlineStr"/>
-      <c r="L4" s="11" t="inlineStr">
+      <c r="K4" s="10" t="n"/>
+      <c r="L4" s="8" t="n"/>
+      <c r="M4" s="11" t="inlineStr">
         <is>
           <t>052_sora2_EVB-Art-Mid-K-CK-C-052.mp4</t>
         </is>
       </c>
-      <c r="M4" s="10" t="inlineStr"/>
-      <c r="N4" s="8" t="inlineStr"/>
-      <c r="O4" s="12" t="inlineStr">
+      <c r="N4" s="10" t="n"/>
+      <c r="O4" s="8" t="n"/>
+      <c r="P4" s="12" t="inlineStr">
         <is>
           <t>052_kling3_EVB-Art-Mid-K-CK-C-052.mp4</t>
         </is>
       </c>
-      <c r="P4" s="10" t="inlineStr"/>
-      <c r="Q4" s="8" t="inlineStr"/>
-      <c r="R4" s="13" t="inlineStr">
+      <c r="Q4" s="10" t="n"/>
+      <c r="R4" s="8" t="n"/>
+      <c r="S4" s="13" t="inlineStr">
         <is>
           <t>052_wan22_EVB-Art-Mid-K-CK-C-052.mp4</t>
         </is>
       </c>
-      <c r="S4" s="10" t="inlineStr"/>
-      <c r="T4" s="8" t="inlineStr"/>
-      <c r="U4" s="14" t="inlineStr">
+      <c r="T4" s="10" t="n"/>
+      <c r="U4" s="8" t="n"/>
+      <c r="V4" s="14" t="inlineStr">
         <is>
           <t>052_wan26_EVB-Art-Mid-K-CK-C-052.mp4</t>
         </is>
       </c>
-      <c r="V4" s="10" t="inlineStr"/>
-      <c r="W4" s="8" t="inlineStr"/>
+      <c r="W4" s="10" t="n"/>
+      <c r="X4" s="8" t="n"/>
     </row>
     <row r="5" ht="60" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
@@ -968,52 +985,56 @@
       <c r="G5" s="8" t="inlineStr">
         <is>
           <t>Answer: Bilateral symmetry with identical left and right halves reflected across a vertical axis
-Key visuals: butterfly outline, vertical axis of symmetry, identical left wing pattern, identical right wing pattern
-Rubric: The video must demonstrate bilateral symmetry through a visual artwork that is clearly symmetric about a vertical axis, with matching details on both sides.</t>
+Key visuals: butterfly outline, vertical axis of symmetry, identical left wing pattern, identical right wing pattern</t>
         </is>
       </c>
       <c r="H5" s="8" t="inlineStr">
+        <is>
+          <t>- The video must demonstrate bilateral symmetry through a visual artwork that is clearly symmetric about a vertical axis, with matching details on both sides.</t>
+        </is>
+      </c>
+      <c r="I5" s="8" t="inlineStr">
         <is>
           <t>- Asymmetric wing patterns
 - No visible axis of symmetry
 - Radial symmetry instead of bilateral</t>
         </is>
       </c>
-      <c r="I5" s="9" t="inlineStr">
+      <c r="J5" s="9" t="inlineStr">
         <is>
           <t>019_veo31_EVB-Art-High-K-CK-C2-019.mp4</t>
         </is>
       </c>
-      <c r="J5" s="10" t="inlineStr"/>
-      <c r="K5" s="8" t="inlineStr"/>
-      <c r="L5" s="11" t="inlineStr">
+      <c r="K5" s="10" t="n"/>
+      <c r="L5" s="8" t="n"/>
+      <c r="M5" s="11" t="inlineStr">
         <is>
           <t>019_sora2_EVB-Art-High-K-CK-C2-019.mp4</t>
         </is>
       </c>
-      <c r="M5" s="10" t="inlineStr"/>
-      <c r="N5" s="8" t="inlineStr"/>
-      <c r="O5" s="12" t="inlineStr">
+      <c r="N5" s="10" t="n"/>
+      <c r="O5" s="8" t="n"/>
+      <c r="P5" s="12" t="inlineStr">
         <is>
           <t>019_kling3_EVB-Art-High-K-CK-C2-019.mp4</t>
         </is>
       </c>
-      <c r="P5" s="10" t="inlineStr"/>
-      <c r="Q5" s="8" t="inlineStr"/>
-      <c r="R5" s="13" t="inlineStr">
+      <c r="Q5" s="10" t="n"/>
+      <c r="R5" s="8" t="n"/>
+      <c r="S5" s="13" t="inlineStr">
         <is>
           <t>019_wan22_EVB-Art-High-K-CK-C2-019.mp4</t>
         </is>
       </c>
-      <c r="S5" s="10" t="inlineStr"/>
-      <c r="T5" s="8" t="inlineStr"/>
-      <c r="U5" s="14" t="inlineStr">
+      <c r="T5" s="10" t="n"/>
+      <c r="U5" s="8" t="n"/>
+      <c r="V5" s="14" t="inlineStr">
         <is>
           <t>019_wan26_EVB-Art-High-K-CK-C2-019.mp4</t>
         </is>
       </c>
-      <c r="V5" s="10" t="inlineStr"/>
-      <c r="W5" s="8" t="inlineStr"/>
+      <c r="W5" s="10" t="n"/>
+      <c r="X5" s="8" t="n"/>
     </row>
     <row r="6" ht="60" customHeight="1">
       <c r="A6" s="7" t="inlineStr">
@@ -1049,52 +1070,56 @@
       <c r="G6" s="8" t="inlineStr">
         <is>
           <t>Answer: In one-point perspective, all receding parallel lines must converge at a single vanishing point on the horizon line
-Key visuals: incorrect drawing with scattered convergence, horizon line, single vanishing point, corrected drawing
-Rubric: The video must clearly show the error (lines not meeting at one point) and the correction (all lines converging to a single vanishing point on the horizon).</t>
+Key visuals: incorrect drawing with scattered convergence, horizon line, single vanishing point, corrected drawing</t>
         </is>
       </c>
       <c r="H6" s="8" t="inlineStr">
+        <is>
+          <t>- The video must clearly show the error (lines not meeting at one point) and the correction (all lines converging to a single vanishing point on the horizon).</t>
+        </is>
+      </c>
+      <c r="I6" s="8" t="inlineStr">
         <is>
           <t>- Not clearly showing the error
 - Corrected version still having multiple vanishing points
 - Missing horizon line</t>
         </is>
       </c>
-      <c r="I6" s="9" t="inlineStr">
+      <c r="J6" s="9" t="inlineStr">
         <is>
           <t>020_veo31_EVB-Art-High-K-CK-M3-020.mp4</t>
         </is>
       </c>
-      <c r="J6" s="10" t="inlineStr"/>
-      <c r="K6" s="8" t="inlineStr"/>
-      <c r="L6" s="11" t="inlineStr">
+      <c r="K6" s="10" t="n"/>
+      <c r="L6" s="8" t="n"/>
+      <c r="M6" s="11" t="inlineStr">
         <is>
           <t>020_sora2_EVB-Art-High-K-CK-M3-020.mp4</t>
         </is>
       </c>
-      <c r="M6" s="10" t="inlineStr"/>
-      <c r="N6" s="8" t="inlineStr"/>
-      <c r="O6" s="12" t="inlineStr">
+      <c r="N6" s="10" t="n"/>
+      <c r="O6" s="8" t="n"/>
+      <c r="P6" s="12" t="inlineStr">
         <is>
           <t>020_kling3_EVB-Art-High-K-CK-M3-020.mp4</t>
         </is>
       </c>
-      <c r="P6" s="10" t="inlineStr"/>
-      <c r="Q6" s="8" t="inlineStr"/>
-      <c r="R6" s="13" t="inlineStr">
+      <c r="Q6" s="10" t="n"/>
+      <c r="R6" s="8" t="n"/>
+      <c r="S6" s="13" t="inlineStr">
         <is>
           <t>020_wan22_EVB-Art-High-K-CK-M3-020.mp4</t>
         </is>
       </c>
-      <c r="S6" s="10" t="inlineStr"/>
-      <c r="T6" s="8" t="inlineStr"/>
-      <c r="U6" s="14" t="inlineStr">
+      <c r="T6" s="10" t="n"/>
+      <c r="U6" s="8" t="n"/>
+      <c r="V6" s="14" t="inlineStr">
         <is>
           <t>020_wan26_EVB-Art-High-K-CK-M3-020.mp4</t>
         </is>
       </c>
-      <c r="V6" s="10" t="inlineStr"/>
-      <c r="W6" s="8" t="inlineStr"/>
+      <c r="W6" s="10" t="n"/>
+      <c r="X6" s="8" t="n"/>
     </row>
     <row r="7" ht="60" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
@@ -1130,52 +1155,56 @@
       <c r="G7" s="8" t="inlineStr">
         <is>
           <t>Answer: Cubism focuses on geometric form and multiple perspectives, analogous to how Impressionism focuses on light and color
-Key visuals: Impressionist style example, Cubist style example, analogy text, key characteristic labels
-Rubric: The video must correctly present the analogy between art movements and their defining characteristics, with visual examples that clearly represent each style.</t>
+Key visuals: Impressionist style example, Cubist style example, analogy text, key characteristic labels</t>
         </is>
       </c>
       <c r="H7" s="8" t="inlineStr">
+        <is>
+          <t>- The video must correctly present the analogy between art movements and their defining characteristics, with visual examples that clearly represent each style.</t>
+        </is>
+      </c>
+      <c r="I7" s="8" t="inlineStr">
         <is>
           <t>- Wrong art movement characteristics
 - Swapped examples
 - Missing visual examples</t>
         </is>
       </c>
-      <c r="I7" s="9" t="inlineStr">
+      <c r="J7" s="9" t="inlineStr">
         <is>
           <t>026_veo31_EVB-Art-Col-K-CK-C3-026.mp4</t>
         </is>
       </c>
-      <c r="J7" s="10" t="inlineStr"/>
-      <c r="K7" s="8" t="inlineStr"/>
-      <c r="L7" s="11" t="inlineStr">
+      <c r="K7" s="10" t="n"/>
+      <c r="L7" s="8" t="n"/>
+      <c r="M7" s="11" t="inlineStr">
         <is>
           <t>026_sora2_EVB-Art-Col-K-CK-C3-026.mp4</t>
         </is>
       </c>
-      <c r="M7" s="10" t="inlineStr"/>
-      <c r="N7" s="8" t="inlineStr"/>
-      <c r="O7" s="12" t="inlineStr">
+      <c r="N7" s="10" t="n"/>
+      <c r="O7" s="8" t="n"/>
+      <c r="P7" s="12" t="inlineStr">
         <is>
           <t>026_kling3_EVB-Art-Col-K-CK-C3-026.mp4</t>
         </is>
       </c>
-      <c r="P7" s="10" t="inlineStr"/>
-      <c r="Q7" s="8" t="inlineStr"/>
-      <c r="R7" s="13" t="inlineStr">
+      <c r="Q7" s="10" t="n"/>
+      <c r="R7" s="8" t="n"/>
+      <c r="S7" s="13" t="inlineStr">
         <is>
           <t>026_wan22_EVB-Art-Col-K-CK-C3-026.mp4</t>
         </is>
       </c>
-      <c r="S7" s="10" t="inlineStr"/>
-      <c r="T7" s="8" t="inlineStr"/>
-      <c r="U7" s="14" t="inlineStr">
+      <c r="T7" s="10" t="n"/>
+      <c r="U7" s="8" t="n"/>
+      <c r="V7" s="14" t="inlineStr">
         <is>
           <t>026_wan26_EVB-Art-Col-K-CK-C3-026.mp4</t>
         </is>
       </c>
-      <c r="V7" s="10" t="inlineStr"/>
-      <c r="W7" s="8" t="inlineStr"/>
+      <c r="W7" s="10" t="n"/>
+      <c r="X7" s="8" t="n"/>
     </row>
     <row r="8" ht="60" customHeight="1">
       <c r="A8" s="7" t="inlineStr">
@@ -1200,7 +1229,7 @@
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>rubric_10pt</t>
+          <t>rubric_5pt</t>
         </is>
       </c>
       <c r="F8" s="8" t="inlineStr">
@@ -1211,46 +1240,61 @@
       <c r="G8" s="8" t="inlineStr">
         <is>
           <t>Answer: Watercolor gradient wash technique from dark to light
-Key visuals: watercolor brush, wet paper surface, concentrated blue pigment, horizontal brush strokes, gradual color transition, dark top to light bottom gradient
-Rubric: 9-10: Technique is clearly demonstrated with correct sequence (wet paper, load brush, progressive dilution), resulting gradient is smooth and visually appealing. 7-8: Technique is mostly correct with minor errors in sequence or dilution, resulting in a mostly smooth gradient with slight unevenness. 5-6: Technique is partially demonstrated with noticeable errors in sequence or dilution, resulting in a somewhat uneven gradient. 3-4: Painting activity shown but gradient technique steps are unclear or result is uneven. 1-2: Technique is poorly demonstrated with incorrect sequence and no clear gradient, resulting in a blotchy or inconsistent appearance.</t>
-        </is>
-      </c>
-      <c r="H8" s="8" t="inlineStr"/>
-      <c r="I8" s="9" t="inlineStr">
+Key visuals: watercolor brush, wet paper surface, concentrated blue pigment, horizontal brush strokes, gradual color transition, dark top to light bottom gradient</t>
+        </is>
+      </c>
+      <c r="H8" s="8" t="inlineStr">
+        <is>
+          <t>- 5: Technique is clearly demonstrated with correct sequence (wet paper, load brush, progressive dilution), resulting gradient is smooth and visually appealing
+- 4: Technique is mostly correct with minor errors in sequence or dilution, resulting in a mostly smooth gradient with slight unevenness
+- 3: Technique is partially demonstrated with noticeable errors in sequence or dilution, resulting in a somewhat uneven gradient
+- 2: Painting activity shown but gradient technique steps are unclear or result is uneven
+- 1: Technique is poorly demonstrated with incorrect sequence and no clear gradient, resulting in a blotchy or inconsistent appearance</t>
+        </is>
+      </c>
+      <c r="I8" s="8" t="inlineStr">
+        <is>
+          <t>- The hand is shown holding a pencil instead of a watercolor brush.
+- The paper is dry when the brush is applied, leading to an incorrect technique demonstration.
+- The pigment applied is a different color than blue, resulting in an inaccurate representation of the technique.
+- The strokes are vertical instead of horizontal, contradicting the prompt's requirements.</t>
+        </is>
+      </c>
+      <c r="J8" s="9" t="inlineStr">
         <is>
           <t>015_veo31_EVB-Art-EHigh-S-PF-D3-015.mp4</t>
         </is>
       </c>
-      <c r="J8" s="10" t="inlineStr"/>
-      <c r="K8" s="8" t="inlineStr"/>
-      <c r="L8" s="11" t="inlineStr">
+      <c r="K8" s="10" t="n"/>
+      <c r="L8" s="8" t="n"/>
+      <c r="M8" s="11" t="inlineStr">
         <is>
           <t>015_sora2_EVB-Art-EHigh-S-PF-D3-015.mp4</t>
         </is>
       </c>
-      <c r="M8" s="10" t="inlineStr"/>
-      <c r="N8" s="8" t="inlineStr"/>
-      <c r="O8" s="12" t="inlineStr">
+      <c r="N8" s="10" t="n"/>
+      <c r="O8" s="8" t="n"/>
+      <c r="P8" s="12" t="inlineStr">
         <is>
           <t>015_kling3_EVB-Art-EHigh-S-PF-D3-015.mp4</t>
         </is>
       </c>
-      <c r="P8" s="10" t="inlineStr"/>
-      <c r="Q8" s="8" t="inlineStr"/>
-      <c r="R8" s="13" t="inlineStr">
+      <c r="Q8" s="10" t="n"/>
+      <c r="R8" s="8" t="n"/>
+      <c r="S8" s="13" t="inlineStr">
         <is>
           <t>015_wan22_EVB-Art-EHigh-S-PF-D3-015.mp4</t>
         </is>
       </c>
-      <c r="S8" s="10" t="inlineStr"/>
-      <c r="T8" s="8" t="inlineStr"/>
-      <c r="U8" s="14" t="inlineStr">
+      <c r="T8" s="10" t="n"/>
+      <c r="U8" s="8" t="n"/>
+      <c r="V8" s="14" t="inlineStr">
         <is>
           <t>015_wan26_EVB-Art-EHigh-S-PF-D3-015.mp4</t>
         </is>
       </c>
-      <c r="V8" s="10" t="inlineStr"/>
-      <c r="W8" s="8" t="inlineStr"/>
+      <c r="W8" s="10" t="n"/>
+      <c r="X8" s="8" t="n"/>
     </row>
     <row r="9" ht="60" customHeight="1">
       <c r="A9" s="7" t="inlineStr">
@@ -1275,7 +1319,7 @@
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>rubric_10pt</t>
+          <t>rubric_5pt</t>
         </is>
       </c>
       <c r="F9" s="8" t="inlineStr">
@@ -1286,46 +1330,61 @@
       <c r="G9" s="8" t="inlineStr">
         <is>
           <t>Answer: Inspirational role model video showing diverse young scientists engaged in research
-Key visuals: modern laboratory setting, diverse young researchers, microscopes and lab equipment, data recording on tablets, whiteboard discussion, collaborative celebration
-Rubric: 9-10: Diverse and relatable young scientists shown actively engaged in research, inspiring and aspirational mood clearly conveyed. 7-8: Young scientists are mostly diverse and engaged, with a generally positive and motivational tone, though some elements may lack clarity. 5-6: Some diversity among young scientists is present, but engagement and inspirational aspects are inconsistent or unclear. 3-4: Laboratory scene present but researchers are not diverse or the inspirational quality is absent. 1-2: Video lacks diversity, engagement, and fails to convey an inspirational or educational message.</t>
-        </is>
-      </c>
-      <c r="H9" s="8" t="inlineStr"/>
-      <c r="I9" s="9" t="inlineStr">
+Key visuals: modern laboratory setting, diverse young researchers, microscopes and lab equipment, data recording on tablets, whiteboard discussion, collaborative celebration</t>
+        </is>
+      </c>
+      <c r="H9" s="8" t="inlineStr">
+        <is>
+          <t>- 5: Diverse and relatable young scientists shown actively engaged in research, inspiring and aspirational mood clearly conveyed
+- 4: Young scientists are mostly diverse and engaged, with a generally positive and motivational tone, though some elements may lack clarity
+- 3: Some diversity among young scientists is present, but engagement and inspirational aspects are inconsistent or unclear
+- 2: Laboratory scene present but researchers are not diverse or the inspirational quality is absent
+- 1: Video lacks diversity, engagement, and fails to convey an inspirational or educational message</t>
+        </is>
+      </c>
+      <c r="I9" s="8" t="inlineStr">
+        <is>
+          <t>- Missing representation of diversity among the young scientists, showing only one gender or ethnicity.
+- Inaccurate depiction of laboratory equipment, such as outdated or incorrect tools.
+- Scientists shown in a chaotic or disorganized lab environment, which does not reflect a modern laboratory setting.
+- Lack of engagement among the scientists, with them appearing disinterested or uninvolved in their research activities.</t>
+        </is>
+      </c>
+      <c r="J9" s="9" t="inlineStr">
         <is>
           <t>012_veo31_EVB-Art-Mid-S-PF-M4-012.mp4</t>
         </is>
       </c>
-      <c r="J9" s="10" t="inlineStr"/>
-      <c r="K9" s="8" t="inlineStr"/>
-      <c r="L9" s="11" t="inlineStr">
+      <c r="K9" s="10" t="n"/>
+      <c r="L9" s="8" t="n"/>
+      <c r="M9" s="11" t="inlineStr">
         <is>
           <t>012_sora2_EVB-Art-Mid-S-PF-M4-012.mp4</t>
         </is>
       </c>
-      <c r="M9" s="10" t="inlineStr"/>
-      <c r="N9" s="8" t="inlineStr"/>
-      <c r="O9" s="12" t="inlineStr">
+      <c r="N9" s="10" t="n"/>
+      <c r="O9" s="8" t="n"/>
+      <c r="P9" s="12" t="inlineStr">
         <is>
           <t>012_kling3_EVB-Art-Mid-S-PF-M4-012.mp4</t>
         </is>
       </c>
-      <c r="P9" s="10" t="inlineStr"/>
-      <c r="Q9" s="8" t="inlineStr"/>
-      <c r="R9" s="13" t="inlineStr">
+      <c r="Q9" s="10" t="n"/>
+      <c r="R9" s="8" t="n"/>
+      <c r="S9" s="13" t="inlineStr">
         <is>
           <t>012_wan22_EVB-Art-Mid-S-PF-M4-012.mp4</t>
         </is>
       </c>
-      <c r="S9" s="10" t="inlineStr"/>
-      <c r="T9" s="8" t="inlineStr"/>
-      <c r="U9" s="14" t="inlineStr">
+      <c r="T9" s="10" t="n"/>
+      <c r="U9" s="8" t="n"/>
+      <c r="V9" s="14" t="inlineStr">
         <is>
           <t>012_wan26_EVB-Art-Mid-S-PF-M4-012.mp4</t>
         </is>
       </c>
-      <c r="V9" s="10" t="inlineStr"/>
-      <c r="W9" s="8" t="inlineStr"/>
+      <c r="W9" s="10" t="n"/>
+      <c r="X9" s="8" t="n"/>
     </row>
     <row r="10" ht="60" customHeight="1">
       <c r="A10" s="7" t="inlineStr">
@@ -1350,7 +1409,7 @@
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>rubric_10pt</t>
+          <t>rubric_5pt</t>
         </is>
       </c>
       <c r="F10" s="8" t="inlineStr">
@@ -1361,46 +1420,61 @@
       <c r="G10" s="8" t="inlineStr">
         <is>
           <t>Answer: Real-world applications of the golden ratio (1:1.618) in architecture, nature, and art composition
-Key visuals: Parthenon facade, golden rectangle overlay, ratio annotation 1:1.618, nautilus shell, golden spiral overlay, painter composing with golden guidelines
-Rubric: 9-10: Golden ratio is accurately depicted with correct proportions, real-world examples are convincing, overlays align well with actual structures. 7-8: Golden ratio is mostly accurate with minor proportional errors, examples are relevant but may lack depth, overlays generally align with structures. 5-6: Golden ratio is somewhat depicted but with noticeable errors, examples are present but not well-explained, overlays partially align with structures. 3-4: Architecture or spiral imagery present but golden ratio proportions are inaccurate or connection is not demonstrated. 1-2: Golden ratio is inaccurately depicted or missing, examples are irrelevant or absent, overlays do not align with structures.</t>
-        </is>
-      </c>
-      <c r="H10" s="8" t="inlineStr"/>
-      <c r="I10" s="9" t="inlineStr">
+Key visuals: Parthenon facade, golden rectangle overlay, ratio annotation 1:1.618, nautilus shell, golden spiral overlay, painter composing with golden guidelines</t>
+        </is>
+      </c>
+      <c r="H10" s="8" t="inlineStr">
+        <is>
+          <t>- 5: Golden ratio is accurately depicted with correct proportions, real-world examples are convincing, overlays align well with actual structures
+- 4: Golden ratio is mostly accurate with minor proportional errors, examples are relevant but may lack depth, overlays generally align with structures
+- 3: Golden ratio is somewhat depicted but with noticeable errors, examples are present but not well-explained, overlays partially align with structures
+- 2: Architecture or spiral imagery present but golden ratio proportions are inaccurate or connection is not demonstrated
+- 1: Golden ratio is inaccurately depicted or missing, examples are irrelevant or absent, overlays do not align with structures</t>
+        </is>
+      </c>
+      <c r="I10" s="8" t="inlineStr">
+        <is>
+          <t>- The Parthenon facade is depicted with incorrect proportions that do not reflect the golden ratio.
+- The golden rectangle overlay is misaligned or poorly scaled, leading to confusion about the ratio.
+- The nautilus shell spiral is inaccurately represented, failing to show the correct curvature of the golden spiral.
+- The video transitions are abrupt and do not effectively connect the different examples of the golden ratio.</t>
+        </is>
+      </c>
+      <c r="J10" s="9" t="inlineStr">
         <is>
           <t>018_veo31_EVB-Art-High-S-PF-C2-018.mp4</t>
         </is>
       </c>
-      <c r="J10" s="10" t="inlineStr"/>
-      <c r="K10" s="8" t="inlineStr"/>
-      <c r="L10" s="11" t="inlineStr">
+      <c r="K10" s="10" t="n"/>
+      <c r="L10" s="8" t="n"/>
+      <c r="M10" s="11" t="inlineStr">
         <is>
           <t>018_sora2_EVB-Art-High-S-PF-C2-018.mp4</t>
         </is>
       </c>
-      <c r="M10" s="10" t="inlineStr"/>
-      <c r="N10" s="8" t="inlineStr"/>
-      <c r="O10" s="12" t="inlineStr">
+      <c r="N10" s="10" t="n"/>
+      <c r="O10" s="8" t="n"/>
+      <c r="P10" s="12" t="inlineStr">
         <is>
           <t>018_kling3_EVB-Art-High-S-PF-C2-018.mp4</t>
         </is>
       </c>
-      <c r="P10" s="10" t="inlineStr"/>
-      <c r="Q10" s="8" t="inlineStr"/>
-      <c r="R10" s="13" t="inlineStr">
+      <c r="Q10" s="10" t="n"/>
+      <c r="R10" s="8" t="n"/>
+      <c r="S10" s="13" t="inlineStr">
         <is>
           <t>018_wan22_EVB-Art-High-S-PF-C2-018.mp4</t>
         </is>
       </c>
-      <c r="S10" s="10" t="inlineStr"/>
-      <c r="T10" s="8" t="inlineStr"/>
-      <c r="U10" s="14" t="inlineStr">
+      <c r="T10" s="10" t="n"/>
+      <c r="U10" s="8" t="n"/>
+      <c r="V10" s="14" t="inlineStr">
         <is>
           <t>018_wan26_EVB-Art-High-S-PF-C2-018.mp4</t>
         </is>
       </c>
-      <c r="V10" s="10" t="inlineStr"/>
-      <c r="W10" s="8" t="inlineStr"/>
+      <c r="W10" s="10" t="n"/>
+      <c r="X10" s="8" t="n"/>
     </row>
     <row r="11" ht="60" customHeight="1">
       <c r="A11" s="7" t="inlineStr">
@@ -1425,7 +1499,7 @@
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
-          <t>rubric_10pt</t>
+          <t>rubric_5pt</t>
         </is>
       </c>
       <c r="F11" s="8" t="inlineStr">
@@ -1436,46 +1510,61 @@
       <c r="G11" s="8" t="inlineStr">
         <is>
           <t>Answer: Visualization of Renaissance linear perspective: vanishing point, horizon line, orthogonal lines demonstrated with architectural scene overlay
-Key visuals: blank canvas with horizon line, vanishing point on horizon, orthogonal lines radiating from vanishing point, transversal lines for depth measurement, architectural scene overlay (tiled floor, buildings), labels for each perspective element, reference to Brunelleschi and Alberti
-Rubric: 9-10: Perspective construction is geometrically accurate, all key elements are correctly labeled, architectural overlay demonstrates convincing depth illusion, historical references are accurate. 7-8: Perspective is mostly accurate with minor errors, most key elements are labeled, architectural scene mostly conveys depth, historical references are mostly correct. 5-6: Perspective has noticeable inaccuracies, several key elements are mislabeled or missing, architectural scene somewhat conveys depth, historical references are vague or partially incorrect. 3-4: Perspective-related imagery present but vanishing point or orthogonal lines are incorrect, or labels are missing. 1-2: Perspective construction is fundamentally flawed, key elements are absent or incorrectly labeled, architectural overlay fails to convey depth, historical references are incorrect or absent.</t>
-        </is>
-      </c>
-      <c r="H11" s="8" t="inlineStr"/>
-      <c r="I11" s="9" t="inlineStr">
+Key visuals: blank canvas with horizon line, vanishing point on horizon, orthogonal lines radiating from vanishing point, transversal lines for depth measurement, architectural scene overlay (tiled floor, buildings), labels for each perspective element, reference to Brunelleschi and Alberti</t>
+        </is>
+      </c>
+      <c r="H11" s="8" t="inlineStr">
+        <is>
+          <t>- 5: Perspective construction is geometrically accurate, all key elements are correctly labeled, architectural overlay demonstrates convincing depth illusion, historical references are accurate
+- 4: Perspective is mostly accurate with minor errors, most key elements are labeled, architectural scene mostly conveys depth, historical references are mostly correct
+- 3: Perspective has noticeable inaccuracies, several key elements are mislabeled or missing, architectural scene somewhat conveys depth, historical references are vague or partially incorrect
+- 2: Perspective-related imagery present but vanishing point or orthogonal lines are incorrect, or labels are missing
+- 1: Perspective construction is fundamentally flawed, key elements are absent or incorrectly labeled, architectural overlay fails to convey depth, historical references are incorrect or absent</t>
+        </is>
+      </c>
+      <c r="I11" s="8" t="inlineStr">
+        <is>
+          <t>- The horizon line is missing or incorrectly placed.
+- The vanishing point is not marked or is inaccurately positioned.
+- Orthogonal lines do not radiate correctly from the vanishing point.
+- The architectural scene overlay lacks historical accuracy or detail.</t>
+        </is>
+      </c>
+      <c r="J11" s="9" t="inlineStr">
         <is>
           <t>028_veo31_EVB-Art-Col-S-PF-V-028.mp4</t>
         </is>
       </c>
-      <c r="J11" s="10" t="inlineStr"/>
-      <c r="K11" s="8" t="inlineStr"/>
-      <c r="L11" s="11" t="inlineStr">
+      <c r="K11" s="10" t="n"/>
+      <c r="L11" s="8" t="n"/>
+      <c r="M11" s="11" t="inlineStr">
         <is>
           <t>028_sora2_EVB-Art-Col-S-PF-V-028.mp4</t>
         </is>
       </c>
-      <c r="M11" s="10" t="inlineStr"/>
-      <c r="N11" s="8" t="inlineStr"/>
-      <c r="O11" s="12" t="inlineStr">
+      <c r="N11" s="10" t="n"/>
+      <c r="O11" s="8" t="n"/>
+      <c r="P11" s="12" t="inlineStr">
         <is>
           <t>028_kling3_EVB-Art-Col-S-PF-V-028.mp4</t>
         </is>
       </c>
-      <c r="P11" s="10" t="inlineStr"/>
-      <c r="Q11" s="8" t="inlineStr"/>
-      <c r="R11" s="13" t="inlineStr">
+      <c r="Q11" s="10" t="n"/>
+      <c r="R11" s="8" t="n"/>
+      <c r="S11" s="13" t="inlineStr">
         <is>
           <t>028_wan22_EVB-Art-Col-S-PF-V-028.mp4</t>
         </is>
       </c>
-      <c r="S11" s="10" t="inlineStr"/>
-      <c r="T11" s="8" t="inlineStr"/>
-      <c r="U11" s="14" t="inlineStr">
+      <c r="T11" s="10" t="n"/>
+      <c r="U11" s="8" t="n"/>
+      <c r="V11" s="14" t="inlineStr">
         <is>
           <t>028_wan26_EVB-Art-Col-S-PF-V-028.mp4</t>
         </is>
       </c>
-      <c r="V11" s="10" t="inlineStr"/>
-      <c r="W11" s="8" t="inlineStr"/>
+      <c r="W11" s="10" t="n"/>
+      <c r="X11" s="8" t="n"/>
     </row>
     <row r="12" ht="60" customHeight="1">
       <c r="A12" s="7" t="inlineStr">
@@ -1500,7 +1589,7 @@
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>rubric_10pt</t>
+          <t>rubric_5pt</t>
         </is>
       </c>
       <c r="F12" s="8" t="inlineStr">
@@ -1511,46 +1600,61 @@
       <c r="G12" s="8" t="inlineStr">
         <is>
           <t>Answer: Step-by-step watercolor gradation technique tutorial for beginners
-Key visuals: watercolor paint set, water cup, thick paper, brush loading paint, dark stripe at top, progressive dilution, light stripe at bottom, step labels
-Rubric: 9-10: All steps clearly shown with correct technique, gradual dilution process is visible, final result shows smooth color transition. 7-8: Most steps are demonstrated clearly, with minor omissions or slight inaccuracies in the dilution process, resulting in a mostly smooth color transition. 5-6: Some steps are shown, but there are noticeable gaps or errors in the technique, leading to an uneven or partially smooth color transition. 3-4: Painting shown but steps are unclear or gradation technique is not properly demonstrated. 1-2: Steps are missing or incorrect, with no visible gradation technique, resulting in a final product that lacks any smooth color transition.</t>
-        </is>
-      </c>
-      <c r="H12" s="8" t="inlineStr"/>
-      <c r="I12" s="9" t="inlineStr">
+Key visuals: watercolor paint set, water cup, thick paper, brush loading paint, dark stripe at top, progressive dilution, light stripe at bottom, step labels</t>
+        </is>
+      </c>
+      <c r="H12" s="8" t="inlineStr">
+        <is>
+          <t>- 5: All steps clearly shown with correct technique, gradual dilution process is visible, final result shows smooth color transition
+- 4: Most steps are demonstrated clearly, with minor omissions or slight inaccuracies in the dilution process, resulting in a mostly smooth color transition
+- 3: Some steps are shown, but there are noticeable gaps or errors in the technique, leading to an uneven or partially smooth color transition
+- 2: Painting shown but steps are unclear or gradation technique is not properly demonstrated
+- 1: Steps are missing or incorrect, with no visible gradation technique, resulting in a final product that lacks any smooth color transition</t>
+        </is>
+      </c>
+      <c r="I12" s="8" t="inlineStr">
+        <is>
+          <t>- Missing the arrangement of watercolor paints, water cup, and thick paper at the beginning
+- Incorrectly showing the brush loading with a light color instead of dark blue paint
+- Failing to demonstrate the progressive dilution of the paint
+- Not depicting the final result with a smooth color transition</t>
+        </is>
+      </c>
+      <c r="J12" s="9" t="inlineStr">
         <is>
           <t>038_veo31_EVB-Art-ELow-S-UC-3b-030.mp4</t>
         </is>
       </c>
-      <c r="J12" s="10" t="inlineStr"/>
-      <c r="K12" s="8" t="inlineStr"/>
-      <c r="L12" s="11" t="inlineStr">
+      <c r="K12" s="10" t="n"/>
+      <c r="L12" s="8" t="n"/>
+      <c r="M12" s="11" t="inlineStr">
         <is>
           <t>038_sora2_EVB-Art-ELow-S-UC-3b-030.mp4</t>
         </is>
       </c>
-      <c r="M12" s="10" t="inlineStr"/>
-      <c r="N12" s="8" t="inlineStr"/>
-      <c r="O12" s="12" t="inlineStr">
+      <c r="N12" s="10" t="n"/>
+      <c r="O12" s="8" t="n"/>
+      <c r="P12" s="12" t="inlineStr">
         <is>
           <t>038_kling3_EVB-Art-ELow-S-UC-3b-030.mp4</t>
         </is>
       </c>
-      <c r="P12" s="10" t="inlineStr"/>
-      <c r="Q12" s="8" t="inlineStr"/>
-      <c r="R12" s="13" t="inlineStr">
+      <c r="Q12" s="10" t="n"/>
+      <c r="R12" s="8" t="n"/>
+      <c r="S12" s="13" t="inlineStr">
         <is>
           <t>038_wan22_EVB-Art-ELow-S-UC-3b-030.mp4</t>
         </is>
       </c>
-      <c r="S12" s="10" t="inlineStr"/>
-      <c r="T12" s="8" t="inlineStr"/>
-      <c r="U12" s="14" t="inlineStr">
+      <c r="T12" s="10" t="n"/>
+      <c r="U12" s="8" t="n"/>
+      <c r="V12" s="14" t="inlineStr">
         <is>
           <t>038_wan26_EVB-Art-ELow-S-UC-3b-030.mp4</t>
         </is>
       </c>
-      <c r="V12" s="10" t="inlineStr"/>
-      <c r="W12" s="8" t="inlineStr"/>
+      <c r="W12" s="10" t="n"/>
+      <c r="X12" s="8" t="n"/>
     </row>
     <row r="13" ht="60" customHeight="1">
       <c r="A13" s="7" t="inlineStr">
@@ -1575,7 +1679,7 @@
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
-          <t>rubric_10pt</t>
+          <t>rubric_5pt</t>
         </is>
       </c>
       <c r="F13" s="8" t="inlineStr">
@@ -1586,46 +1690,61 @@
       <c r="G13" s="8" t="inlineStr">
         <is>
           <t>Answer: Instructor-based lecture on visual composition principles: rule of thirds, leading lines, and balance with photographic and painting examples
-Key visuals: instructor at display with examples, 3x3 grid overlay on landscape photograph, key elements at grid intersections, converging leading lines in photograph, focal point identification, symmetrical vs asymmetrical balance comparison, visual weight indicators, principle labels
-Rubric: 9-10: All three composition principles are accurately explained with clear visual examples, grid overlay and leading lines are correctly demonstrated, balance comparison is insightful, instructor delivery is engaging. 7-8: Most principles are explained accurately with good visual examples, grid overlay and leading lines are mostly correct, balance comparison is present but lacks depth, instructor delivery is mostly engaging. 5-6: Some principles are explained with basic visual examples, grid overlay and leading lines are partially correct, balance comparison is minimal, instructor delivery is somewhat engaging. 3-4: Composition-related imagery shown but principles are incorrectly explained or visual examples do not clearly illustrate the concepts. 1-2: Principles are poorly explained with little to no visual examples, grid overlay and leading lines are incorrect or missing, balance comparison is absent, instructor delivery is disengaging.</t>
-        </is>
-      </c>
-      <c r="H13" s="8" t="inlineStr"/>
-      <c r="I13" s="9" t="inlineStr">
+Key visuals: instructor at display with examples, 3x3 grid overlay on landscape photograph, key elements at grid intersections, converging leading lines in photograph, focal point identification, symmetrical vs asymmetrical balance comparison, visual weight indicators, principle labels</t>
+        </is>
+      </c>
+      <c r="H13" s="8" t="inlineStr">
+        <is>
+          <t>- 5: All three composition principles are accurately explained with clear visual examples, grid overlay and leading lines are correctly demonstrated, balance comparison is insightful, instructor delivery is engaging
+- 4: Most principles are explained accurately with good visual examples, grid overlay and leading lines are mostly correct, balance comparison is present but lacks depth, instructor delivery is mostly engaging
+- 3: Some principles are explained with basic visual examples, grid overlay and leading lines are partially correct, balance comparison is minimal, instructor delivery is somewhat engaging
+- 2: Composition-related imagery shown but principles are incorrectly explained or visual examples do not clearly illustrate the concepts
+- 1: Principles are poorly explained with little to no visual examples, grid overlay and leading lines are incorrect or missing, balance comparison is absent, instructor delivery is disengaging</t>
+        </is>
+      </c>
+      <c r="I13" s="8" t="inlineStr">
+        <is>
+          <t>- The instructor fails to overlay the 3x3 grid on the example images, making the rule of thirds unclear.
+- Visual examples do not include relevant photographs or paintings that illustrate the leading lines principle.
+- The balance comparison is not visually represented, leaving the explanation incomplete.
+- The instructor's explanations are inaccurate or lack clarity, leading to confusion about the principles.</t>
+        </is>
+      </c>
+      <c r="J13" s="9" t="inlineStr">
         <is>
           <t>062_veo31_EVB-Art-High-S-UC-2-054.mp4</t>
         </is>
       </c>
-      <c r="J13" s="10" t="inlineStr"/>
-      <c r="K13" s="8" t="inlineStr"/>
-      <c r="L13" s="11" t="inlineStr">
+      <c r="K13" s="10" t="n"/>
+      <c r="L13" s="8" t="n"/>
+      <c r="M13" s="11" t="inlineStr">
         <is>
           <t>062_sora2_EVB-Art-High-S-UC-2-054.mp4</t>
         </is>
       </c>
-      <c r="M13" s="10" t="inlineStr"/>
-      <c r="N13" s="8" t="inlineStr"/>
-      <c r="O13" s="12" t="inlineStr">
+      <c r="N13" s="10" t="n"/>
+      <c r="O13" s="8" t="n"/>
+      <c r="P13" s="12" t="inlineStr">
         <is>
           <t>062_kling3_EVB-Art-High-S-UC-2-054.mp4</t>
         </is>
       </c>
-      <c r="P13" s="10" t="inlineStr"/>
-      <c r="Q13" s="8" t="inlineStr"/>
-      <c r="R13" s="13" t="inlineStr">
+      <c r="Q13" s="10" t="n"/>
+      <c r="R13" s="8" t="n"/>
+      <c r="S13" s="13" t="inlineStr">
         <is>
           <t>062_wan22_EVB-Art-High-S-UC-2-054.mp4</t>
         </is>
       </c>
-      <c r="S13" s="10" t="inlineStr"/>
-      <c r="T13" s="8" t="inlineStr"/>
-      <c r="U13" s="14" t="inlineStr">
+      <c r="T13" s="10" t="n"/>
+      <c r="U13" s="8" t="n"/>
+      <c r="V13" s="14" t="inlineStr">
         <is>
           <t>062_wan26_EVB-Art-High-S-UC-2-054.mp4</t>
         </is>
       </c>
-      <c r="V13" s="10" t="inlineStr"/>
-      <c r="W13" s="8" t="inlineStr"/>
+      <c r="W13" s="10" t="n"/>
+      <c r="X13" s="8" t="n"/>
     </row>
     <row r="14" ht="60" customHeight="1">
       <c r="A14" s="7" t="inlineStr">
@@ -1650,7 +1769,7 @@
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>rubric_10pt</t>
+          <t>rubric_5pt</t>
         </is>
       </c>
       <c r="F14" s="8" t="inlineStr">
@@ -1661,46 +1780,61 @@
       <c r="G14" s="8" t="inlineStr">
         <is>
           <t>Answer: Step-by-step origami crane folding tutorial
-Key visuals: square paper sheet, diagonal fold creases, preliminary base, petal folds, bird base, neck and tail shaping, reverse fold for head, completed crane with spread wings, step labels
-Rubric: 9-10: All origami folds shown in correct sequence, paper manipulation is clear and followable, final crane shape is accurate and recognizable. 7-8: Most folds are shown in sequence, with minor omissions or slight inaccuracies, but the final crane is mostly recognizable. 5-6: Several key steps are missing or out of order, making it difficult to follow, and the final crane is only partially recognizable. 3-4: Paper folding shown but steps are missing, out of order, or final shape does not resemble a crane. 1-2: Few or no steps are shown correctly, making it impossible to follow, and the final shape is unrecognizable as a crane.</t>
-        </is>
-      </c>
-      <c r="H14" s="8" t="inlineStr"/>
-      <c r="I14" s="9" t="inlineStr">
+Key visuals: square paper sheet, diagonal fold creases, preliminary base, petal folds, bird base, neck and tail shaping, reverse fold for head, completed crane with spread wings, step labels</t>
+        </is>
+      </c>
+      <c r="H14" s="8" t="inlineStr">
+        <is>
+          <t>- 5: All origami folds shown in correct sequence, paper manipulation is clear and followable, final crane shape is accurate and recognizable
+- 4: Most folds are shown in sequence, with minor omissions or slight inaccuracies, but the final crane is mostly recognizable
+- 3: Several key steps are missing or out of order, making it difficult to follow, and the final crane is only partially recognizable
+- 2: Paper folding shown but steps are missing, out of order, or final shape does not resemble a crane
+- 1: Few or no steps are shown correctly, making it impossible to follow, and the final shape is unrecognizable as a crane</t>
+        </is>
+      </c>
+      <c r="I14" s="8" t="inlineStr">
+        <is>
+          <t>- Missing the initial diagonal folds, leading to incorrect creases
+- Incorrectly demonstrating the petal folds, resulting in a distorted bird base
+- Failing to show the reverse fold for the head, leaving the crane incomplete
+- Using a non-square sheet of paper, which confuses the folding process</t>
+        </is>
+      </c>
+      <c r="J14" s="9" t="inlineStr">
         <is>
           <t>040_veo31_EVB-Art-Col-S-UC-3d-032.mp4</t>
         </is>
       </c>
-      <c r="J14" s="10" t="inlineStr"/>
-      <c r="K14" s="8" t="inlineStr"/>
-      <c r="L14" s="11" t="inlineStr">
+      <c r="K14" s="10" t="n"/>
+      <c r="L14" s="8" t="n"/>
+      <c r="M14" s="11" t="inlineStr">
         <is>
           <t>040_sora2_EVB-Art-Col-S-UC-3d-032.mp4</t>
         </is>
       </c>
-      <c r="M14" s="10" t="inlineStr"/>
-      <c r="N14" s="8" t="inlineStr"/>
-      <c r="O14" s="12" t="inlineStr">
+      <c r="N14" s="10" t="n"/>
+      <c r="O14" s="8" t="n"/>
+      <c r="P14" s="12" t="inlineStr">
         <is>
           <t>040_kling3_EVB-Art-Col-S-UC-3d-032.mp4</t>
         </is>
       </c>
-      <c r="P14" s="10" t="inlineStr"/>
-      <c r="Q14" s="8" t="inlineStr"/>
-      <c r="R14" s="13" t="inlineStr">
+      <c r="Q14" s="10" t="n"/>
+      <c r="R14" s="8" t="n"/>
+      <c r="S14" s="13" t="inlineStr">
         <is>
           <t>040_wan22_EVB-Art-Col-S-UC-3d-032.mp4</t>
         </is>
       </c>
-      <c r="S14" s="10" t="inlineStr"/>
-      <c r="T14" s="8" t="inlineStr"/>
-      <c r="U14" s="14" t="inlineStr">
+      <c r="T14" s="10" t="n"/>
+      <c r="U14" s="8" t="n"/>
+      <c r="V14" s="14" t="inlineStr">
         <is>
           <t>040_wan26_EVB-Art-Col-S-UC-3d-032.mp4</t>
         </is>
       </c>
-      <c r="V14" s="10" t="inlineStr"/>
-      <c r="W14" s="8" t="inlineStr"/>
+      <c r="W14" s="10" t="n"/>
+      <c r="X14" s="8" t="n"/>
     </row>
     <row r="15" ht="60" customHeight="1">
       <c r="A15" s="7" t="inlineStr">
@@ -1725,7 +1859,7 @@
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
-          <t>vlm_comparison</t>
+          <t>rubric_5pt</t>
         </is>
       </c>
       <c r="F15" s="8" t="inlineStr">
@@ -1736,54 +1870,64 @@
       <c r="G15" s="8" t="inlineStr">
         <is>
           <t>Answer: The color becomes lighter and more transparent (the intensity decreases)
-Key visuals: brush with concentrated paint, adding water to brush, gradient from dark to light, transparency increasing
-Rubric: Compare VLM accuracy rate with video vs. text-only baseline. Positive delta indicates video aids conceptual understanding of art techniques.</t>
-        </is>
-      </c>
-      <c r="H15" s="8" t="inlineStr"/>
-      <c r="I15" s="9" t="inlineStr">
+Key visuals: brush with concentrated paint, adding water to brush, gradient from dark to light, transparency increasing</t>
+        </is>
+      </c>
+      <c r="H15" s="8" t="inlineStr">
+        <is>
+          <t>- Compare VLM accuracy rate with video vs. text-only baseline. Positive delta indicates video aids conceptual understanding of art techniques.</t>
+        </is>
+      </c>
+      <c r="I15" s="8" t="inlineStr">
+        <is>
+          <t>- The brush is depicted with dry paint instead of concentrated paint.
+- The gradient shown does not transition from dark to light, or is inaccurately represented.
+- The water being added is not visually clear, leading to confusion about the effect on color intensity.</t>
+        </is>
+      </c>
+      <c r="J15" s="9" t="inlineStr">
         <is>
           <t>066_veo31_EVB-Art-EHigh-S-VIU-U2-048.mp4</t>
         </is>
       </c>
-      <c r="J15" s="10" t="inlineStr"/>
-      <c r="K15" s="8" t="inlineStr"/>
-      <c r="L15" s="11" t="inlineStr">
+      <c r="K15" s="10" t="n"/>
+      <c r="L15" s="8" t="n"/>
+      <c r="M15" s="11" t="inlineStr">
         <is>
           <t>066_sora2_EVB-Art-EHigh-S-VIU-U2-048.mp4</t>
         </is>
       </c>
-      <c r="M15" s="10" t="inlineStr"/>
-      <c r="N15" s="8" t="inlineStr"/>
-      <c r="O15" s="12" t="inlineStr">
+      <c r="N15" s="10" t="n"/>
+      <c r="O15" s="8" t="n"/>
+      <c r="P15" s="12" t="inlineStr">
         <is>
           <t>066_kling3_EVB-Art-EHigh-S-VIU-U2-048.mp4</t>
         </is>
       </c>
-      <c r="P15" s="10" t="inlineStr"/>
-      <c r="Q15" s="8" t="inlineStr"/>
-      <c r="R15" s="13" t="inlineStr">
+      <c r="Q15" s="10" t="n"/>
+      <c r="R15" s="8" t="n"/>
+      <c r="S15" s="13" t="inlineStr">
         <is>
           <t>066_wan22_EVB-Art-EHigh-S-VIU-U2-048.mp4</t>
         </is>
       </c>
-      <c r="S15" s="10" t="inlineStr"/>
-      <c r="T15" s="8" t="inlineStr"/>
-      <c r="U15" s="14" t="inlineStr">
+      <c r="T15" s="10" t="n"/>
+      <c r="U15" s="8" t="n"/>
+      <c r="V15" s="14" t="inlineStr">
         <is>
           <t>066_wan26_EVB-Art-EHigh-S-VIU-U2-048.mp4</t>
         </is>
       </c>
-      <c r="V15" s="10" t="inlineStr"/>
-      <c r="W15" s="8" t="inlineStr"/>
+      <c r="W15" s="10" t="n"/>
+      <c r="X15" s="8" t="n"/>
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation sqref="J2 J3 J4 J5 J6 J7 M2 M3 M4 M5 M6 M7 P2 P3 P4 P5 P6 P7 S2 S3 S4 S5 S6 S7 V2 V3 V4 V5 V6 V7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid score" error="Enter 0, 0.5, or 1" promptTitle="exact_match" prompt="0=Wrong, 0.5=Partial, 1=Correct" type="list">
+    <dataValidation sqref="K2 K3 K4 K5 K6 K7 N2 N3 N4 N5 N6 N7 Q2 Q3 Q4 Q5 Q6 Q7 T2 T3 T4 T5 T6 T7 W2 W3 W4 W5 W6 W7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="0, 0.5, 1 중 하나를 입력하세요" type="list">
       <formula1>"0,0.5,1"</formula1>
     </dataValidation>
-    <dataValidation sqref="J8 J9 J10 J11 J12 J13 J14 J15 M8 M9 M10 M11 M12 M13 M14 M15 P8 P9 P10 P11 P12 P13 P14 P15 S8 S9 S10 S11 S12 S13 S14 S15 V8 V9 V10 V11 V12 V13 V14 V15" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid score" error="Enter a number between 1 and 10" promptTitle="rubric_10pt" prompt="1-2: Very Poor, 3-4: Poor, 5-6: Adequate, 7-8: Good, 9-10: Excellent" type="list">
-      <formula1>"1,2,3,4,5,6,7,8,9,10"</formula1>
+    <dataValidation sqref="K8 K9 K10 K11 K12 K13 K14 K15 N8 N9 N10 N11 N12 N13 N14 N15 Q8 Q9 Q10 Q11 Q12 Q13 Q14 Q15 T8 T9 T10 T11 T12 T13 T14 T15 W8 W9 W10 W11 W12 W13 W14 W15" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="1~5 사이의 정수를 입력하세요" type="list">
+      <formula1>"1,2,3,4,5"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
